--- a/InputData/elec/BTC/BAU Transmission Capacity.xlsx
+++ b/InputData/elec/BTC/BAU Transmission Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us-analysis\InputData\elec\BTC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\KY\elec\BTC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7EED0E4-3621-4CED-AA03-E0C0C4F7BD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17C90A5B-BE5D-4776-A19D-BCBCABDE5494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1800" yWindow="1800" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>BTC BAU Transmission Capacity</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>BAU Transmission Capacity (MW-miles)</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
   </si>
 </sst>
 </file>
@@ -242,7 +245,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -261,6 +264,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -336,9 +340,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -376,9 +380,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -411,26 +415,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -463,26 +450,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -656,18 +626,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="2" max="2" width="42.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="10">
+        <v>45237</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -675,65 +651,65 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
       <c r="B4" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B5" s="6">
         <v>2021</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
       <c r="B6" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="44.25" x14ac:dyDescent="0.75">
       <c r="B7" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B8" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B9" s="5"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B10" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B11" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B12" s="6">
         <v>2012</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B13" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B14" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B15" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B16" s="5"/>
     </row>
   </sheetData>
@@ -748,53 +724,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AO36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="36.453125" customWidth="1"/>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -806,7 +782,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -818,7 +794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -830,12 +806,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -846,7 +822,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -857,7 +833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -869,7 +845,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.75">
       <c r="A21">
         <v>2010</v>
       </c>
@@ -878,7 +854,7 @@
         <v>175000000</v>
       </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.75">
       <c r="A22">
         <v>2050</v>
       </c>
@@ -887,7 +863,7 @@
         <v>180319148.93617022</v>
       </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.75">
       <c r="A24">
         <v>2010</v>
       </c>
@@ -1012,7 +988,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.75">
       <c r="A25" s="2" cm="1">
         <f t="array" ref="A25">TREND($B$21:$B$22,$A$21:$A$22,A24)</f>
         <v>175000000</v>
@@ -1178,12 +1154,12 @@
         <v>180319148.93617022</v>
       </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -1192,7 +1168,7 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.75">
       <c r="A31">
         <v>2020</v>
       </c>
@@ -1287,7 +1263,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.75">
       <c r="A32" s="2">
         <f>B29</f>
         <v>150000000</v>
@@ -1413,10 +1389,10 @@
         <v>153393665.15837106</v>
       </c>
     </row>
-    <row r="34" spans="11:21" x14ac:dyDescent="0.35">
+    <row r="34" spans="11:21" x14ac:dyDescent="0.75">
       <c r="U34" s="2"/>
     </row>
-    <row r="36" spans="11:21" x14ac:dyDescent="0.35">
+    <row r="36" spans="11:21" x14ac:dyDescent="0.75">
       <c r="K36" s="9"/>
     </row>
   </sheetData>
@@ -1428,13 +1404,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A8E9EE-75BB-4C67-BE26-F56AE2DF869D}">
   <dimension ref="A1:AF13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="31.453125" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -1443,7 +1419,7 @@
         <v>17000000</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -1452,7 +1428,7 @@
         <v>33000000000</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1461,7 +1437,7 @@
         <v>2500000000</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A4" s="5" t="s">
         <v>29</v>
       </c>
@@ -1471,17 +1447,17 @@
       </c>
       <c r="D4" s="9"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.75">
       <c r="B9">
         <v>2020</v>
       </c>
@@ -1576,7 +1552,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1703,7 +1679,7 @@
         <v>1287878.7878787876</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.75">
       <c r="K13" s="9"/>
     </row>
   </sheetData>
@@ -1717,13 +1693,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="32" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.75">
       <c r="B1">
         <v>2020</v>
       </c>
@@ -1818,7 +1794,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1947,7 +1923,7 @@
         <v>154681543.94624984</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.75">
       <c r="L4" s="3"/>
     </row>
   </sheetData>
